--- a/template/t11_ocr_report.xlsx
+++ b/template/t11_ocr_report.xlsx
@@ -79,7 +79,7 @@
     <t>micro_0008_SⅡ.jpg</t>
   </si>
   <si>
-    <t>micro_0012_SI.jpg</t>
+    <t>micro_0009_O_S1.jpg</t>
   </si>
   <si>
     <t>micro_0004_SF.jpg</t>
@@ -577,7 +577,7 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -627,7 +627,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -677,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -727,7 +727,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -744,7 +744,7 @@
         <v>34</v>
       </c>
       <c r="C6">
-        <v>0.8026884198188782</v>
+        <v>0.933626651763916</v>
       </c>
       <c r="D6" t="s">
         <v>44</v>
@@ -777,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>35</v>
       </c>
       <c r="C7">
-        <v>0.9678190946578979</v>
+        <v>0.9629496932029724</v>
       </c>
       <c r="D7" t="s">
         <v>44</v>
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -965,19 +965,19 @@
         <v>45</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -1015,19 +1015,19 @@
         <v>45</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11">
         <v>0</v>
